--- a/healthcare_forms/005_mental_health_journal_template--healthcare_forms.xlsx
+++ b/healthcare_forms/005_mental_health_journal_template--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input_1</t>
+          <t>daily_mood_rating</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>daily_mood_rating</t>
+          <t>Daily Mood Rating (1-10)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>mental_health_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mental_health_status</t>
+          <t>Mental Health Status</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_input_3</t>
+          <t>mental_health_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mental_health_progress</t>
+          <t>Progress Notes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_input_4</t>
+          <t>emotions_today</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mental_health_notes</t>
+          <t>Emotions Today</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,41 +612,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_input_5</t>
+          <t>emotions_over_2_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>emotions_today</t>
+          <t>Emotions Over Last 2 Days</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_input_6</t>
+          <t>mental_health_goal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>emotions_over_2_days</t>
+          <t>Mental Health Goal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_input_7</t>
+          <t>mental_health_goal_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mental_health_goal</t>
+          <t>Goal Status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_input_8</t>
+          <t>mental_health_rating</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mental_health_goal_status</t>
+          <t>Mental Health Rating (1-10)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_input_9</t>
+          <t>mental_health_rating_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mental_health_rating</t>
+          <t>Mental Health Rating 2 (1-10)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_input_10</t>
+          <t>mental_health_rater_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mental_health_rating_2</t>
+          <t>Mental Health Rater 1 (Good/Fair)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mental_health_rating_3</t>
+          <t>mental_health_rater_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mental_health_rating_2</t>
+          <t>Mental Health Rater 2 (Good/Fair)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_input_12</t>
+          <t>mental_health_rater_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mental_health_rater_2</t>
+          <t>Mental Health Rater 3 (Good/Fair)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_input_13</t>
+          <t>mental_health_rater_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mental_health_rater_3</t>
+          <t>Mental Health Rater 4 (Good/Fair)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_input_14</t>
+          <t>mental_health_rater_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mental_health_rater_4</t>
+          <t>Mental Health Rater 5 (Good/Fair)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>user_input_15</t>
+          <t>mental_health_rater_6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mental_health_rater_5</t>
+          <t>Mental Health Rater 6 (Good/Fair)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mental_health_rater_6</t>
+          <t>mental_health_rater_7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mental_health_rater_5</t>
+          <t>Mental Health Rater 7 (Good/Fair)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_input_17</t>
+          <t>mental_health_rater_8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mental_health_rater_6</t>
+          <t>Mental Health Rater 8 (Good/Fair)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_input_18</t>
+          <t>mental_health_rater_9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mental_health_rater_7</t>
+          <t>Mental Health Rater 9 (Good/Fair)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>user_input_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>mental_health_rater_8</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>user_input_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>mental_health_rater_8</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>user_input_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>mental_health_rater_8</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mental_health_rater_9</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>mental_health_rater_8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>mental_health_rater_10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>mental_health_rater_9</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>user_input_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>mental_health_rater_11</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>user_input_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>mental_health_rater_12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_input_2_choices</t>
+          <t>mental_health_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_input_2_choices</t>
+          <t>mental_health_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,245 +999,245 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>emotions_today_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Happy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>emotions_today_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_input_6_choices</t>
+          <t>emotions_today_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_input_6_choices</t>
+          <t>emotions_today_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_input_7_choices</t>
+          <t>emotions_today_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excited</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_input_7_choices</t>
+          <t>emotions_over_2_days_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Happy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>emotions_over_2_days_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>emotions_over_2_days_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_input_12_choices</t>
+          <t>emotions_over_2_days_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_input_12_choices</t>
+          <t>emotions_over_2_days_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Excited</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>mental_health_goal_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>mental_health_goal_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_input_14_choices</t>
+          <t>mental_health_goal_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_input_14_choices</t>
+          <t>mental_health_goal_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>mental_health_rater_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>mental_health_rater_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1271,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mental_health_rater_6_choices</t>
+          <t>mental_health_rater_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1288,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mental_health_rater_6_choices</t>
+          <t>mental_health_rater_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1305,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>mental_health_rater_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1322,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>mental_health_rater_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1339,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>user_input_18_choices</t>
+          <t>mental_health_rater_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1356,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>user_input_18_choices</t>
+          <t>mental_health_rater_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1373,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>user_input_19_choices</t>
+          <t>mental_health_rater_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1390,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>user_input_19_choices</t>
+          <t>mental_health_rater_5_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1407,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_input_20_choices</t>
+          <t>mental_health_rater_6_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1424,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_input_20_choices</t>
+          <t>mental_health_rater_6_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1441,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_input_21_choices</t>
+          <t>mental_health_rater_7_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1458,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>user_input_21_choices</t>
+          <t>mental_health_rater_7_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1475,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mental_health_rater_9_choices</t>
+          <t>mental_health_rater_8_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1492,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mental_health_rater_9_choices</t>
+          <t>mental_health_rater_8_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1509,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mental_health_rater_10_choices</t>
+          <t>mental_health_rater_9_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1526,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mental_health_rater_10_choices</t>
+          <t>mental_health_rater_9_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1696,74 +1535,6 @@
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>user_input_24_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>user_input_24_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>user_input_25_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>user_input_25_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
